--- a/target/classes/templates/transcript_template_letterhead_space.xlsx
+++ b/target/classes/templates/transcript_template_letterhead_space.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\scheduler\src\main\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C84F9D56-D17E-4105-BD6E-68DC4E0B00CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCDE59AC-17D3-4BBD-A350-9D2A750F2157}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
